--- a/evaluation_results.xlsx
+++ b/evaluation_results.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Plain Language Scores" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Accuracy Scores" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,7 +491,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>46.38461538461539</v>
+        <v>51</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -502,10 +503,10 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>7.384615384615385</v>
+        <v>12</v>
       </c>
       <c r="H2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -514,7 +515,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L2" t="n">
         <v>15</v>
@@ -523,19 +524,19 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HB0002</t>
+          <t>HB0001</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>58.70379032258065</v>
+        <v>55.25</v>
       </c>
       <c r="D3" t="n">
-        <v>4.953790322580652</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
@@ -547,16 +548,16 @@
         <v>12</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>6.75</v>
+        <v>8.25</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L3" t="n">
         <v>15</v>
@@ -565,7 +566,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HB0003</t>
+          <t>HB0002</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -574,7 +575,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>40.33333333333334</v>
+        <v>47</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -586,10 +587,10 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>5.333333333333334</v>
+        <v>12</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -598,7 +599,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L4" t="n">
         <v>15</v>
@@ -607,19 +608,19 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HB0004</t>
+          <t>HB0002</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>59.74595588235295</v>
+        <v>47</v>
       </c>
       <c r="D5" t="n">
-        <v>8.245955882352952</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
@@ -634,7 +635,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -649,7 +650,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HB0006</t>
+          <t>HB0003</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -658,10 +659,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>47</v>
+        <v>63.70982336956523</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>8.709823369565228</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
@@ -673,7 +674,7 @@
         <v>12</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -691,19 +692,19 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HB0009</t>
+          <t>HB0003</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>36.11111111111111</v>
+        <v>47.34097374608152</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>5.000064655172423</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
@@ -712,13 +713,13 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1.09090909090909</v>
       </c>
       <c r="H7" t="n">
-        <v>3.111111111111111</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -733,7 +734,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HB0010</t>
+          <t>HB0004</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -742,7 +743,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -757,7 +758,7 @@
         <v>12</v>
       </c>
       <c r="H8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -769,25 +770,25 @@
         <v>10</v>
       </c>
       <c r="L8" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HB0011</t>
+          <t>HB0004</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>55</v>
+        <v>45.47633928571429</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>4.101339285714289</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
@@ -796,13 +797,13 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>6.375</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -817,7 +818,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HB0012</t>
+          <t>HB0005</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -826,7 +827,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>47.76923076923077</v>
+        <v>42.5</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -838,10 +839,10 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>12</v>
+        <v>4.5</v>
       </c>
       <c r="H10" t="n">
-        <v>2.769230769230769</v>
+        <v>7</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -850,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L10" t="n">
         <v>15</v>
@@ -859,19 +860,19 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HB0013</t>
+          <t>HB0005</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>48.905</v>
+        <v>44.92337301587303</v>
       </c>
       <c r="D11" t="n">
-        <v>1.619285714285716</v>
+        <v>3.601944444444449</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
@@ -880,19 +881,19 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>6.285714285714286</v>
+        <v>0.5714285714285721</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>9.75</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L11" t="n">
         <v>15</v>
@@ -901,7 +902,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HB0001</t>
+          <t>HB0006</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -910,7 +911,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -922,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -934,7 +935,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L12" t="n">
         <v>15</v>
@@ -943,19 +944,19 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HB0002</t>
+          <t>HB0006</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
+        <v>63.66714147286822</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>0.1671414728682166</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
@@ -967,10 +968,10 @@
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -985,7 +986,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HB0004</t>
+          <t>HB0007</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1027,16 +1028,16 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HB0005</t>
+          <t>HB0007</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>54.20879120879121</v>
+        <v>57.98611111111111</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -1045,22 +1046,22 @@
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>1.208791208791208</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
         <v>12</v>
       </c>
       <c r="H15" t="n">
-        <v>8</v>
+        <v>3.111111111111111</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>7.875</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L15" t="n">
         <v>15</v>
@@ -1069,7 +1070,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HB0007</t>
+          <t>HB0008</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1078,7 +1079,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -1102,7 +1103,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L16" t="n">
         <v>15</v>
@@ -1111,19 +1112,19 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HB0013</t>
+          <t>HB0008</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>63.58323529411766</v>
+        <v>51.0904752316858</v>
       </c>
       <c r="D17" t="n">
-        <v>7.583235294117657</v>
+        <v>4.312066140776707</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
@@ -1132,19 +1133,19 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1.09090909090909</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>15</v>
+        <v>10.6875</v>
       </c>
       <c r="J17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L17" t="n">
         <v>15</v>
@@ -1153,7 +1154,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HB0016</t>
+          <t>HB0009</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1162,10 +1163,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>53.14333333333335</v>
+        <v>55</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8100000000000094</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
@@ -1177,7 +1178,7 @@
         <v>12</v>
       </c>
       <c r="H18" t="n">
-        <v>5.333333333333334</v>
+        <v>8</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1195,19 +1196,19 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HB0017</t>
+          <t>HB0009</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>36.33333333333334</v>
+        <v>65.91018382352942</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>0.0351838235294224</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
@@ -1216,19 +1217,19 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>5.333333333333334</v>
+        <v>12</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>10.875</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L19" t="n">
         <v>15</v>
@@ -1237,7 +1238,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HB0019</t>
+          <t>HB0010</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1246,10 +1247,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>90.15125</v>
+        <v>55</v>
       </c>
       <c r="D20" t="n">
-        <v>11.65125</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>10</v>
@@ -1264,10 +1265,10 @@
         <v>8</v>
       </c>
       <c r="I20" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>10</v>
@@ -1279,19 +1280,19 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HB0022</t>
+          <t>HB0010</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>55</v>
+        <v>61.33903769841271</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>0.408482142857153</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
@@ -1303,10 +1304,10 @@
         <v>12</v>
       </c>
       <c r="H21" t="n">
-        <v>8</v>
+        <v>7.555555555555555</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>6.375</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1318,844 +1319,420 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Bill Number</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Groundedness</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Groundedness Reason</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Relevance</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Relevance Reason</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Interpretation</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Interpretation Reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>HB0001</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>human</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>49.76923076923077</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>10</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>12</v>
-      </c>
-      <c r="H22" t="n">
-        <v>2.769230769230769</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>10</v>
-      </c>
-      <c r="L22" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>The summary includes specific examples of expenditures (entertainment, office renovations, and travel) that are not contained in the provided source text or metadata. The source material only refers to 'certain types of expenditures' and 'reasonable cost limitations' without listing specific categories.</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>The summary successfully identifies the core components of the bill: the 110% cap on supervisor compensation recovery, the requirement for utilities to adopt cost-limiting policies, the entities affected, and the PSC's role in publishing guidance.</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>The summary accurately reflects the bill's mandates and prohibitions as described in the title and legislative purpose, correctly identifying the 'prohibits' and 'requires' aspects of the text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>HB0002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>The summary mentions an age requirement of 55 years old which is not contained in the provided bill text or metadata (the text snippet cuts off right before the age is specified).</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>The summary identifies the core change and the population affected, but omits the effective date found in the metadata (taxable years beginning after December 31, 2025).</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>The summary accurately interprets the increase in the subtraction modification from $15,000 to $20,000 for the specified classes of retired public safety employees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>HB0003</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>human</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>47.11111111111111</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>10</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>12</v>
-      </c>
-      <c r="H23" t="n">
-        <v>3.111111111111111</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>10</v>
-      </c>
-      <c r="L23" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>The summary accurately reflects the contents of the bill, including the tuition exemption for dependents of public safety employees and the changes to the Conroy and Cryor scholarship programs. Although the full text of the scholarship changes is truncated in the provided snippet, the metadata and bill title explicitly mention 'altering the method for allocating funds' for these specific programs.</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>The summary identifies the two primary pillars of the bill: the tuition waiver for survivors of fallen public safety employees and the restructuring of specific scholarship programs. It includes details about the allocation formula and priority for renewal applicants, which are critical administrative components.</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>The summary correctly interprets the transition of the scholarship programs from an entitlement-style allocation to a capped system based on a formula, which is the standard legal interpretation of 'altering the method for allocating funds' in this specific legislative context (HB0003).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>HB0004</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>human</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>55</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>10</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>12</v>
-      </c>
-      <c r="H24" t="n">
-        <v>8</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>10</v>
-      </c>
-      <c r="L24" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>The summary accurately reflects the change from a 'model year of 1999 or earlier' to 'at least 25 years old' as seen in the bill text, and the reinstatement provision found in the bill's title.</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>The summary captures the most important aspects of the bill: the change in eligibility criteria and the mandate for the MVA to reinstate certain registrations.</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>The summary correctly interprets the shift from a static date to a rolling age requirement and accurately captures the administrative requirement regarding previous law changes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>HB0005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>The summary includes specific details—the 50% credit amount, the seven-year claim period, and the fourth-year start date—that are not found in the provided bill text or metadata. While these may be in the full bill, they are not in the source material provided for evaluation.</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>The summary captures the core purpose and the specific taxes involved. However, it omits the $18,750,000 annual credit limit and the recapture provisions, both of which are explicitly mentioned in the metadata as material provisions.</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>The summary correctly identifies the bill as an establishment of a program and identifies the correct administering agency and tax types. It does not conflate authorization with requirement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>HB0006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>The summary includes specific details regarding the contents of the support plans (referrals to childcare, healthcare, and government programs) that are not contained in the provided bill text or metadata. It correctly identifies the exclusion of the University of Maryland Global Campus.</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>The summary covers the main functional areas of the bill but omits the specific reporting deadline of September 1, 2027, which is a material provision noted in the metadata.</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>The summary misinterprets the scope of the plan requirement. It states that public institutions (plural/general) must adopt plans, whereas the bill's metadata and the preamble's strike-throughs indicate the mandate to adopt a plan was specifically limited to community colleges, while the data collection requirement applied more broadly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>HB0007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>The summary is almost entirely grounded in the bill's metadata and text, but it includes one specific detail—that the license is for completing 'the required examination'—which is not present in the provided source material (which only refers to 'certain licensing requirements').</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>The summary captures the core purpose of the bill, identifies the governing board, specifies who is affected (applicants for licensure), and notes the key condition of the license (supervision).</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>The summary accurately interprets the bill as an authorization for the Board to issue a new type of license and correctly identifies the supervisory relationship required by the act.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>HB0008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>The summary includes several specific details that are not present in the provided 3000 characters of bill text or metadata, including the '12-month period' for citations, 'fee waivers for low-income drivers', and 'potential vehicle impoundment'. While these are likely in the full bill, they are not grounded in the provided source material.</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>The summary identifies the core purpose, the administrative body (MVA), the specific requirements for drivers, the timeline for compliance, and the penalties for non-compliance.</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>The summary accurately interprets the bill as a proposal (using 'establishes') and correctly identifies the mandatory nature of the course and the conditional nature of the registration suspension.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>HB0009</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>human</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>41</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="n">
-        <v>10</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="n">
-        <v>12</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>10</v>
-      </c>
-      <c r="L25" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>HB0011</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>human</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>26</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="n">
-        <v>10</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>4</v>
-      </c>
-      <c r="L26" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>HB0012</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>human</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>42</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" t="n">
-        <v>10</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="n">
-        <v>6</v>
-      </c>
-      <c r="H27" t="n">
-        <v>8</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>6</v>
-      </c>
-      <c r="L27" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>HB0015</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>human</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>64.25</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" t="n">
-        <v>10</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" t="n">
-        <v>12</v>
-      </c>
-      <c r="H28" t="n">
-        <v>8</v>
-      </c>
-      <c r="I28" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>8</v>
-      </c>
-      <c r="L28" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>HB0018</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>human</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>44</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" t="n">
-        <v>10</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="n">
-        <v>12</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>10</v>
-      </c>
-      <c r="L29" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>HB0019</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>human</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>47.88888888888889</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="n">
-        <v>10</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="n">
-        <v>5.333333333333334</v>
-      </c>
-      <c r="H30" t="n">
-        <v>7.555555555555555</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
-        <v>10</v>
-      </c>
-      <c r="L30" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>HB0022</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>human</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>55</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" t="n">
-        <v>10</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="n">
-        <v>12</v>
-      </c>
-      <c r="H31" t="n">
-        <v>8</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>10</v>
-      </c>
-      <c r="L31" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>HB0001</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>human</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>51</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" t="n">
-        <v>10</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" t="n">
-        <v>12</v>
-      </c>
-      <c r="H32" t="n">
-        <v>4</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
-        <v>10</v>
-      </c>
-      <c r="L32" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>HB0002</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>human</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>49</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" t="n">
-        <v>10</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" t="n">
-        <v>12</v>
-      </c>
-      <c r="H33" t="n">
-        <v>2</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
-        <v>10</v>
-      </c>
-      <c r="L33" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>HB0003</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>human</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>63.70982336956523</v>
-      </c>
-      <c r="D34" t="n">
-        <v>8.709823369565228</v>
-      </c>
-      <c r="E34" t="n">
-        <v>10</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" t="n">
-        <v>12</v>
-      </c>
-      <c r="H34" t="n">
-        <v>8</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>10</v>
-      </c>
-      <c r="L34" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>HB0004</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>human</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>47</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" t="n">
-        <v>10</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" t="n">
-        <v>12</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
-        <v>10</v>
-      </c>
-      <c r="L35" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>HB0005</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>human</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" t="n">
-        <v>10</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H36" t="n">
-        <v>7</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>8</v>
-      </c>
-      <c r="L36" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>HB0006</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>human</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>55</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" t="n">
-        <v>10</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" t="n">
-        <v>12</v>
-      </c>
-      <c r="H37" t="n">
-        <v>8</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="n">
-        <v>10</v>
-      </c>
-      <c r="L37" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>HB0007</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>human</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>55</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" t="n">
-        <v>10</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" t="n">
-        <v>12</v>
-      </c>
-      <c r="H38" t="n">
-        <v>8</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="n">
-        <v>10</v>
-      </c>
-      <c r="L38" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>HB0008</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>human</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>55</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" t="n">
-        <v>10</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" t="n">
-        <v>12</v>
-      </c>
-      <c r="H39" t="n">
-        <v>8</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="n">
-        <v>10</v>
-      </c>
-      <c r="L39" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>HB0009</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>human</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>55</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" t="n">
-        <v>10</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" t="n">
-        <v>12</v>
-      </c>
-      <c r="H40" t="n">
-        <v>8</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" t="n">
-        <v>10</v>
-      </c>
-      <c r="L40" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>The summary mentions a 'four-county pilot,' but the provided bill text and metadata only refer to 'certain counties.' The specific number 'four' is not present in the source material provided.</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>The summary effectively covers the main provisions: the creation of the Oversight Board, the use of AI (chatbots/voicebots), the purpose of the program, and the phased expansion from specific counties to the whole state.</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>The summary accurately interprets the bill's intent to establish a program and an oversight body, correctly identifying the mandatory nature of the expansion and the specific technologies involved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>HB0010</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>human</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>55</v>
-      </c>
-      <c r="D41" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" t="n">
-        <v>10</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" t="n">
-        <v>12</v>
-      </c>
-      <c r="H41" t="n">
-        <v>8</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" t="n">
-        <v>10</v>
-      </c>
-      <c r="L41" t="n">
-        <v>15</v>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>The summary accurately reflects the text and metadata. It mentions the expansion of the definition of 'newspaper' to include digital-only publications, the requirement for coverage in more than three counties, the employment of staff for local news, the publication frequency, and the requirement for a public archive.</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>The summary captures the material provisions of the bill, including the core definition change and the specific qualifications required for digital publications to carry legal notices.</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>5</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>The summary correctly interprets the bill as an expansion of existing definitions and accurately lists the conditions for digital publications without conflating requirements or status.</t>
+        </is>
       </c>
     </row>
   </sheetData>
